--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488036_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488036_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>20.3052</v>
+        <v>20.6099</v>
       </c>
       <c r="E2" t="n">
-        <v>19.0071</v>
+        <v>19.1714</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2981</v>
+        <v>1.4385</v>
       </c>
       <c r="G2" t="n">
         <v>13.3934</v>
@@ -610,13 +610,13 @@
         <v>3.3698</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1743</v>
+        <v>0.1304</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1103</v>
+        <v>0.2746</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2846</v>
+        <v>-0.1442</v>
       </c>
       <c r="V2" t="n">
         <v>5.6986</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9627</v>
+        <v>1.508</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9583</v>
+        <v>1.508</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9956</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4008</v>
+        <v>1.508</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3352</v>
+        <v>0.3027</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0656</v>
+        <v>1.2053</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6599</v>
+        <v>1.508</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7358</v>
+        <v>0.3027</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9241</v>
+        <v>1.2053</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2591</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4007</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1415</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5113</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.014</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4973</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1476</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.508</v>
+        <v>1.2449</v>
       </c>
       <c r="E4" t="n">
-        <v>1.508</v>
+        <v>-0.2698</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.5147</v>
       </c>
       <c r="G4" t="n">
-        <v>1.508</v>
+        <v>-1.6893</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3027</v>
+        <v>-1.2323</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2053</v>
+        <v>-0.457</v>
       </c>
       <c r="J4" t="n">
-        <v>1.508</v>
+        <v>-0.4437</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3027</v>
+        <v>0.2963</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2053</v>
+        <v>-0.74</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.2456</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.5286</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.2551</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.0421</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.213</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2048</v>
+        <v>1.0964</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2272</v>
+        <v>-0.7772</v>
       </c>
       <c r="F5" t="n">
-        <v>3.432</v>
+        <v>1.8736</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3668</v>
+        <v>-0.4151</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7294</v>
+        <v>-0.9794</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0962</v>
+        <v>0.5643</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9354</v>
+        <v>0.3689</v>
       </c>
       <c r="K5" t="n">
-        <v>0.128</v>
+        <v>0.0876</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8074</v>
+        <v>0.2812</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5686</v>
+        <v>-0.7839</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.067</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2888</v>
+        <v>0.2831</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1716</v>
+        <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3226</v>
+        <v>-0.0743</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5064</v>
+        <v>-0.155</v>
       </c>
       <c r="U5" t="n">
-        <v>0.829</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8198</v>
+        <v>0.8812</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9415</v>
+        <v>-1.9611</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7613</v>
+        <v>2.8423</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4151</v>
+        <v>0.3668</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9794</v>
+        <v>-0.7294</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5643</v>
+        <v>1.0962</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3689</v>
+        <v>0.9354</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0876</v>
+        <v>0.128</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2812</v>
+        <v>0.8074</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7839</v>
+        <v>-0.5686</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.067</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2831</v>
+        <v>0.2888</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5769</v>
+        <v>3.1716</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3509</v>
+        <v>-0.0009</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3192</v>
+        <v>-0.2403</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0316</v>
+        <v>0.2393</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0515</v>
+        <v>0.7454</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3509</v>
+        <v>1.8814</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4024</v>
+        <v>-1.136</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6893</v>
+        <v>1.4008</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2323</v>
+        <v>0.3352</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.457</v>
+        <v>1.0656</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4437</v>
+        <v>2.6599</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2963</v>
+        <v>1.7358</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.74</v>
+        <v>0.9241</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2456</v>
+        <v>-1.2591</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5286</v>
+        <v>-1.4007</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2831</v>
+        <v>0.1415</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9822</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9733</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4485</v>
+        <v>1.2941</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1232</v>
+        <v>0.9372</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3254</v>
+        <v>0.3569</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2071</v>
+        <v>-2.1476</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0184</v>
+        <v>0.5249</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2496</v>
+        <v>-0.2886</v>
       </c>
       <c r="F8" t="n">
-        <v>2.268</v>
+        <v>0.8136</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.624</v>
+        <v>-0.4819</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7898</v>
+        <v>-2.0527</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8341</v>
+        <v>1.5708</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9099</v>
+        <v>0.0361</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7927</v>
+        <v>-1.2574</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1172</v>
+        <v>1.2935</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7141</v>
+        <v>-0.518</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9971</v>
+        <v>-0.7953</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2831</v>
+        <v>0.2774</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9733</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7108</v>
+        <v>-0.2441</v>
       </c>
       <c r="T8" t="n">
-        <v>1.039</v>
+        <v>-0.3247</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3283</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9405</v>
+        <v>-0.5331</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.337</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2037</v>
+        <v>0.4138</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1356</v>
+        <v>-1.462</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9319</v>
+        <v>1.8758</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1382</v>
@@ -1156,13 +1156,13 @@
         <v>3.3698</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1864</v>
+        <v>-0.569</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1232</v>
+        <v>-0.4495</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0633</v>
+        <v>-0.1195</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>I. MARTIN ARROYO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.261</v>
+        <v>-0.2029</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9623</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7012</v>
+        <v>0.3964</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4819</v>
+        <v>-0.6388</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0527</v>
+        <v>-0.6388</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5708</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0361</v>
+        <v>-0.6388</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2574</v>
+        <v>-0.6388</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2935</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.518</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7953</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2774</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.03</v>
+        <v>0.0395</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9984</v>
+        <v>0.0395</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0316</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MARTIN ARROYO</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3047</v>
+        <v>-0.6675</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7012</v>
+        <v>-3.104</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3964</v>
+        <v>2.4365</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6388</v>
+        <v>-2.624</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6388</v>
+        <v>-1.7898</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.8341</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6388</v>
+        <v>-1.9099</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6388</v>
+        <v>-0.7927</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.1172</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.7141</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.9971</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3964</v>
+        <v>0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3964</v>
+        <v>2.9733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0624</v>
+        <v>0.0248</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0624</v>
+        <v>0.1846</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.1598</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1801</v>
+        <v>-1.7263</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1989</v>
+        <v>-1.0629</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0188</v>
+        <v>-0.6634</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8012</v>
+        <v>-1.9676</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0399</v>
+        <v>-1.3076</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7613</v>
+        <v>-0.6599</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2094</v>
+        <v>-1.2496</v>
       </c>
       <c r="K12" t="n">
         <v>-0.5782</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6312</v>
+        <v>-0.6713</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5918</v>
+        <v>-0.718</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4617</v>
+        <v>-0.7294</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1301</v>
+        <v>0.0114</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6806</v>
+        <v>-0.5011</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0072</v>
+        <v>-0.0293</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6878</v>
+        <v>-0.4718</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2666</v>
+        <v>0.9405</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X12" t="n">
         <v>-0.2666</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3023</v>
+        <v>-2.1843</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4704</v>
+        <v>-3.0346</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8319</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.9676</v>
+        <v>-1.8012</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3076</v>
+        <v>-1.0399</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6599</v>
+        <v>-0.7613</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2496</v>
+        <v>-1.2094</v>
       </c>
       <c r="K13" t="n">
         <v>-0.5782</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6713</v>
+        <v>-0.6312</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.718</v>
+        <v>-0.5918</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7294</v>
+        <v>-0.4617</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0114</v>
+        <v>-0.1301</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.077</v>
+        <v>0.6764</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4368</v>
+        <v>0.157</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6402</v>
+        <v>0.5193</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>-0.2666</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.9724</v>
+        <v>-2.9733</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.8929</v>
+        <v>-4.0343</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9206</v>
+        <v>1.061</v>
       </c>
       <c r="G14" t="n">
         <v>-2.7239</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6921</v>
+        <v>0.6911</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3599</v>
+        <v>0.2186</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3322</v>
+        <v>0.4725</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9405</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.6462</v>
+        <v>19.2702</v>
       </c>
       <c r="E15" t="n">
-        <v>5.342900000000001</v>
+        <v>5.966999999999997</v>
       </c>
       <c r="F15" t="n">
-        <v>13.3032</v>
+        <v>13.3033</v>
       </c>
       <c r="G15" t="n">
-        <v>4.189000000000002</v>
+        <v>4.188999999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.400700000000001</v>
+        <v>-8.400699999999999</v>
       </c>
       <c r="I15" t="n">
         <v>12.5899</v>
@@ -1600,7 +1600,7 @@
         <v>14.0069</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5685</v>
+        <v>3.568499999999999</v>
       </c>
       <c r="L15" t="n">
         <v>10.4386</v>
@@ -1624,19 +1624,19 @@
         <v>26.76</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5878999999999999</v>
+        <v>1.2118</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.05360000000000026</v>
+        <v>0.5706000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6413</v>
+        <v>0.6411000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>3.958299999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>8.238500000000002</v>
+        <v>8.2385</v>
       </c>
       <c r="X15" t="n">
         <v>-4.2803</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6054</v>
+        <v>4.8786</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4575</v>
+        <v>4.1519</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1479</v>
+        <v>0.7268</v>
       </c>
       <c r="G16" t="n">
         <v>3.4935</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9048</v>
+        <v>0.178</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0589</v>
+        <v>-0.2467</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8458</v>
+        <v>0.4246</v>
       </c>
       <c r="V16" t="n">
         <v>1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3315</v>
+        <v>3.2224</v>
       </c>
       <c r="E17" t="n">
-        <v>5.5362</v>
+        <v>5.2306</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2047</v>
+        <v>-2.0082</v>
       </c>
       <c r="G17" t="n">
         <v>4.5671</v>
@@ -1780,13 +1780,13 @@
         <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0576</v>
+        <v>-0.0515</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7967</v>
+        <v>0.4911</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7391</v>
+        <v>-0.5425</v>
       </c>
       <c r="V17" t="n">
         <v>-2.6808</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1225</v>
+        <v>-0.9187</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0352</v>
+        <v>-0.8315</v>
       </c>
       <c r="F19" t="n">
         <v>-0.0873</v>
@@ -1936,10 +1936,10 @@
         <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2203</v>
+        <v>-0.0165</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1248</v>
+        <v>0.0789</v>
       </c>
       <c r="U19" t="n">
         <v>-0.0955</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MONTES EGEA</t>
+          <t>D. GUAITA MACHADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4942</v>
+        <v>-1.3634</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0132</v>
+        <v>-0.6826</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4811</v>
+        <v>-0.6807</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2876</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4291</v>
+        <v>0.9842</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1415</v>
+        <v>-1.5996</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0404</v>
+        <v>1.817</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0404</v>
+        <v>1.1703</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.328</v>
+        <v>-2.4324</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4695</v>
+        <v>-0.1861</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1415</v>
+        <v>-2.2463</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7929</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4137</v>
+        <v>-0.1533</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>-0.5174</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3513</v>
+        <v>0.3641</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. GUAITA MACHADO</t>
+          <t>P. MONTES EGEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6304</v>
+        <v>-1.41</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0901</v>
+        <v>-1.0132</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5403</v>
+        <v>-0.3968</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.2876</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9842</v>
+        <v>-0.4291</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5996</v>
+        <v>0.1415</v>
       </c>
       <c r="J21" t="n">
-        <v>1.817</v>
+        <v>0.0404</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1703</v>
+        <v>0.0404</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6467000000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4324</v>
+        <v>-0.328</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1861</v>
+        <v>-0.4695</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2463</v>
+        <v>0.1415</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4204</v>
+        <v>-0.3295</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.0624</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5044999999999999</v>
+        <v>-0.2671</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RAMIREZ GUERRA-LIBRERO</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.792</v>
+        <v>-1.4828</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7862</v>
+        <v>-1.6587</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0058</v>
+        <v>0.1758</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3886</v>
+        <v>-3.2124</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4036</v>
+        <v>1.1688</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7922</v>
+        <v>-4.3812</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3298</v>
+        <v>-1.3386</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3298</v>
+        <v>0.8077</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-2.1463</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7184</v>
+        <v>-1.8738</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0738</v>
+        <v>0.3612</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7922</v>
+        <v>-2.2349</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8087</v>
+        <v>-0.1249</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1248</v>
+        <v>-0.3201</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6839</v>
+        <v>0.1952</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>J. RAMIREZ GUERRA-LIBRERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4839</v>
+        <v>-1.4936</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5755</v>
+        <v>-0.6843</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0916</v>
+        <v>-0.8093</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2124</v>
+        <v>-0.3886</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1688</v>
+        <v>0.4036</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.3812</v>
+        <v>-0.7922</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3386</v>
+        <v>0.3298</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8077</v>
+        <v>0.3298</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1463</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8738</v>
+        <v>-0.7184</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3612</v>
+        <v>0.0738</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2349</v>
+        <v>-0.7922</v>
       </c>
       <c r="P23" t="n">
-        <v>1.784</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1259</v>
+        <v>-0.5103</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2369</v>
+        <v>-0.0229</v>
       </c>
       <c r="U23" t="n">
-        <v>0.111</v>
+        <v>-0.4874</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5153</v>
+        <v>-2.7014</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.564</v>
+        <v>-3.6659</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0487</v>
+        <v>0.9644</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6965</v>
@@ -2326,13 +2326,13 @@
         <v>2.3787</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1627</v>
+        <v>-0.3488</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0586</v>
+        <v>-0.1605</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1041</v>
+        <v>-0.1883</v>
       </c>
       <c r="V24" t="n">
         <v>-0.0704</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2417</v>
+        <v>-5.4292</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.726</v>
+        <v>-4.7725</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5157</v>
+        <v>-0.6566</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4217</v>
+        <v>-3.891</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7392</v>
+        <v>-1.6486</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3175</v>
+        <v>-2.2424</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5582</v>
+        <v>-1.3267</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5984</v>
+        <v>-0.6515</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0402</v>
+        <v>-0.6752</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-2.5643</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1408</v>
+        <v>-0.9971</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2774</v>
+        <v>-1.5672</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5769</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1711</v>
+        <v>-0.3488</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7967</v>
+        <v>-0.4725</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3744</v>
+        <v>0.1237</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8334</v>
+        <v>-6.0567</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.4856</v>
+        <v>-4.541</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3478</v>
+        <v>-1.5157</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.891</v>
+        <v>-1.4217</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6486</v>
+        <v>-1.7392</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.2424</v>
+        <v>0.3175</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3267</v>
+        <v>-0.5582</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6515</v>
+        <v>-0.5984</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6752</v>
+        <v>0.0402</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.5643</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9971</v>
+        <v>-1.1408</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.5672</v>
+        <v>0.2774</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1893</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R26" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.753</v>
+        <v>0.3561</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1855</v>
+        <v>-0.0183</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4325</v>
+        <v>0.3744</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.6777</v>
+        <v>-7.0996</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.2291</v>
+        <v>-6.0441</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4486</v>
+        <v>-1.0555</v>
       </c>
       <c r="G27" t="n">
         <v>-2.6371</v>
@@ -2560,13 +2560,13 @@
         <v>2.7751</v>
       </c>
       <c r="S27" t="n">
-        <v>1.1835</v>
+        <v>0.7617</v>
       </c>
       <c r="T27" t="n">
-        <v>1.4244</v>
+        <v>0.6095</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2409</v>
+        <v>0.1522</v>
       </c>
       <c r="V27" t="n">
         <v>-0.0704</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-18.6462</v>
+        <v>-18.6464</v>
       </c>
       <c r="E28" t="n">
-        <v>-13.3032</v>
+        <v>-13.3033</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.3431</v>
+        <v>-5.343100000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-4.1892</v>
@@ -2638,13 +2638,13 @@
         <v>16.8489</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.5877000000000003</v>
+        <v>-0.5877999999999997</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6412000000000002</v>
+        <v>-0.6412999999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>0.05340000000000006</v>
+        <v>0.05339999999999995</v>
       </c>
       <c r="V28" t="n">
         <v>-3.9583</v>
